--- a/data/GPS/Metricas_GPS 4.xlsx
+++ b/data/GPS/Metricas_GPS 4.xlsx
@@ -1,18 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\GPS\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_227EA04E15204F85A83C430C95FC410FE97BF631" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{237059D5-D5FD-4BF0-82AB-6C2C1C63641D}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="_ib" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="_synced_data" sheetId="2" r:id="rId6"/>
+    <sheet name="_ib" sheetId="1" r:id="rId1"/>
+    <sheet name="_synced_data" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
   <si>
     <t>eJy9lltv2jAUx7+KladNQiGElWXTNIkN9WUto53arruoMrZDXHyJYru0IL77bMO6kAErmZqn5Jwcn/P7H9+yCDDURAVvwSLQ0j+cw74EcRT3oiRKghYI7iBzLuZidbC0nrSQ/KnhLj6/0yiduELfF2vjhmIXxY3BcE57ycwNRZKtg+zbOmIuZtR9y6HOnO1LWls/5KRsC8i9fUxQBp3DCKqdwxGXE7LIarXfqbqZePoUMkWsoyDYIJ9DS+1LwAkm6WpYp3f0pmt9RBhuPR7zZwkrlyokOSqT2eFlDk5FmXNgCoioFFW8Y3h2Wdbr40tZcwYfSFHONJR8XJB9kr+dxx+DTViqXe29eUc2Cq2jdmXG1Nxubea4MCojj236795iqvb0dso3WkuVhgJRCGwxuxorzJ+yq2SDWRfmOZDngoSvaoK/B50ETHk7q8Kf9EzWFHyvJrylj49aMdgq4DO/OG1KwOuaAlz/46SVbFdwJuF9c1OAhN6jYOMc+GGiaAzBl7ygQivw4t2fWXj51zoSH/pNiIAIOR1xDR19RBhZHZIWqMLfOf/ayCbGpDb/gCi4T8LFUF0fdnby1cKrMQfh76E77qa2aquyhj4KwSm8pxxWqdGI4AOpVxdfLWoqDqEekJ3YedrtNtJsleN/NNvtx42L9tJDV4kH8fXw2a9WeqtCJvETV/bI/yOAEwlxsHRpEKNE6FUpYRjzzsd9QGbgShbTsZTTYPkLMWMQcA==</t>
   </si>
@@ -90,9 +99,6 @@
   </si>
   <si>
     <t xml:space="preserve">Jorge_vicaria </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alejandro_Garcia_Gumiel </t>
   </si>
   <si>
     <t xml:space="preserve">Gonzalo_Echavarria </t>
@@ -128,25 +134,26 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="17.0"/>
+      <sz val="17"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -157,38 +164,43 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -196,7 +208,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -386,22 +398,25 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -410,21 +425,22 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:O14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="6" max="7" width="22.25"/>
+    <col min="6" max="7" width="22.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -471,12 +487,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
-        <v>46242.0</v>
+        <v>46242</v>
       </c>
       <c r="B2" s="2">
-        <v>112.031</v>
+        <v>112.03100000000001</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>18</v>
@@ -488,28 +504,28 @@
         <v>4.282</v>
       </c>
       <c r="F2" s="2">
-        <v>0.349</v>
+        <v>0.34899999999999998</v>
       </c>
       <c r="G2" s="2">
-        <v>0.012</v>
+        <v>1.2E-2</v>
       </c>
       <c r="H2" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J2" s="2">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="K2" s="2">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="L2" s="2">
         <v>5.39</v>
       </c>
       <c r="M2" s="2">
-        <v>-6.419</v>
+        <v>-6.4189999999999996</v>
       </c>
       <c r="N2" s="2">
         <v>27.54</v>
@@ -518,9 +534,9 @@
         <v>910.1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>46242.0</v>
+        <v>46242</v>
       </c>
       <c r="B3" s="2">
         <v>111.917</v>
@@ -532,45 +548,45 @@
         <v>21</v>
       </c>
       <c r="E3" s="2">
-        <v>4.773</v>
+        <v>4.7729999999999997</v>
       </c>
       <c r="F3" s="2">
         <v>0.371</v>
       </c>
       <c r="G3" s="2">
-        <v>0.011</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="H3" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J3" s="2">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="K3" s="2">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="L3" s="2">
-        <v>4.938</v>
+        <v>4.9379999999999997</v>
       </c>
       <c r="M3" s="2">
-        <v>-5.212</v>
+        <v>-5.2119999999999997</v>
       </c>
       <c r="N3" s="2">
-        <v>26.845</v>
+        <v>26.844999999999999</v>
       </c>
       <c r="O3" s="2">
         <v>877.6</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>46242.0</v>
+        <v>46242</v>
       </c>
       <c r="B4" s="2">
-        <v>113.695</v>
+        <v>113.69499999999999</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>22</v>
@@ -579,31 +595,31 @@
         <v>21</v>
       </c>
       <c r="E4" s="2">
-        <v>5.155</v>
+        <v>5.1550000000000002</v>
       </c>
       <c r="F4" s="2">
-        <v>0.424</v>
+        <v>0.42399999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>0.069</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="H4" s="2">
-        <v>0.009</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="I4" s="2">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="J4" s="2">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="K4" s="2">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="L4" s="2">
-        <v>5.104</v>
+        <v>5.1040000000000001</v>
       </c>
       <c r="M4" s="2">
-        <v>-5.062</v>
+        <v>-5.0620000000000003</v>
       </c>
       <c r="N4" s="2">
         <v>30.334</v>
@@ -612,9 +628,9 @@
         <v>839.9</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>46242.0</v>
+        <v>46242</v>
       </c>
       <c r="B5" s="2">
         <v>112.217</v>
@@ -626,42 +642,42 @@
         <v>24</v>
       </c>
       <c r="E5" s="2">
-        <v>5.433</v>
+        <v>5.4329999999999998</v>
       </c>
       <c r="F5" s="2">
-        <v>0.264</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>0.001</v>
+        <v>1E-3</v>
       </c>
       <c r="H5" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="K5" s="2">
-        <v>41.0</v>
+        <v>41</v>
       </c>
       <c r="L5" s="2">
-        <v>5.305</v>
+        <v>5.3049999999999997</v>
       </c>
       <c r="M5" s="2">
-        <v>-5.792</v>
+        <v>-5.7919999999999998</v>
       </c>
       <c r="N5" s="2">
-        <v>25.315</v>
+        <v>25.315000000000001</v>
       </c>
       <c r="O5" s="2">
         <v>1014.5</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>46242.0</v>
+        <v>46242</v>
       </c>
       <c r="B6" s="2">
         <v>112.98</v>
@@ -673,31 +689,31 @@
         <v>21</v>
       </c>
       <c r="E6" s="2">
-        <v>4.837</v>
+        <v>4.8369999999999997</v>
       </c>
       <c r="F6" s="2">
-        <v>0.212</v>
+        <v>0.21199999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>0.033</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="H6" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="J6" s="2">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="K6" s="2">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="L6" s="2">
         <v>5.133</v>
       </c>
       <c r="M6" s="2">
-        <v>-4.583</v>
+        <v>-4.5830000000000002</v>
       </c>
       <c r="N6" s="2">
         <v>27.997</v>
@@ -706,247 +722,247 @@
         <v>917.3</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>46242.0</v>
+        <v>46242</v>
       </c>
       <c r="B7" s="2">
-        <v>111.852</v>
+        <v>112.256</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E7" s="2">
-        <v>4.612</v>
+        <v>5.1130000000000004</v>
       </c>
       <c r="F7" s="2">
-        <v>0.214</v>
+        <v>0.39100000000000001</v>
       </c>
       <c r="G7" s="2">
-        <v>0.012</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="H7" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>2.0</v>
+        <v>3</v>
       </c>
       <c r="J7" s="2">
-        <v>22.0</v>
+        <v>47</v>
       </c>
       <c r="K7" s="2">
-        <v>17.0</v>
+        <v>41</v>
       </c>
       <c r="L7" s="2">
-        <v>4.578</v>
+        <v>5.5590000000000002</v>
       </c>
       <c r="M7" s="2">
-        <v>-4.505</v>
+        <v>-6</v>
       </c>
       <c r="N7" s="2">
-        <v>26.572</v>
+        <v>26.309000000000001</v>
       </c>
       <c r="O7" s="2">
-        <v>914.8</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>746.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>46242.0</v>
+        <v>46242</v>
       </c>
       <c r="B8" s="2">
-        <v>112.256</v>
+        <v>113.795</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="E8" s="2">
-        <v>5.113</v>
+        <v>3.4140000000000001</v>
       </c>
       <c r="F8" s="2">
-        <v>0.391</v>
+        <v>0.19</v>
       </c>
       <c r="G8" s="2">
-        <v>0.015</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="H8" s="2">
-        <v>0.0</v>
+        <v>1E-3</v>
       </c>
       <c r="I8" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J8" s="2">
-        <v>47.0</v>
+        <v>22</v>
       </c>
       <c r="K8" s="2">
-        <v>41.0</v>
+        <v>14</v>
       </c>
       <c r="L8" s="2">
-        <v>5.559</v>
+        <v>5.1310000000000002</v>
       </c>
       <c r="M8" s="2">
-        <v>-6.0</v>
+        <v>-4.9870000000000001</v>
       </c>
       <c r="N8" s="2">
-        <v>26.309</v>
+        <v>28.885999999999999</v>
       </c>
       <c r="O8" s="2">
-        <v>746.3</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>618.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>46242.0</v>
+        <v>46242</v>
       </c>
       <c r="B9" s="2">
-        <v>113.795</v>
+        <v>111.142</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E9" s="2">
-        <v>3.414</v>
+        <v>6.3949999999999996</v>
       </c>
       <c r="F9" s="2">
-        <v>0.19</v>
+        <v>0.72299999999999998</v>
       </c>
       <c r="G9" s="2">
-        <v>0.036</v>
+        <v>8.8999999999999996E-2</v>
       </c>
       <c r="H9" s="2">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>3.0</v>
+        <v>7</v>
       </c>
       <c r="J9" s="2">
-        <v>22.0</v>
+        <v>33</v>
       </c>
       <c r="K9" s="2">
-        <v>14.0</v>
+        <v>35</v>
       </c>
       <c r="L9" s="2">
-        <v>5.131</v>
+        <v>4.3029999999999999</v>
       </c>
       <c r="M9" s="2">
-        <v>-4.987</v>
+        <v>-5.6870000000000003</v>
       </c>
       <c r="N9" s="2">
-        <v>28.886</v>
+        <v>28.745999999999999</v>
       </c>
       <c r="O9" s="2">
-        <v>618.6</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>1337.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>46242.0</v>
+        <v>46242</v>
       </c>
       <c r="B10" s="2">
-        <v>111.142</v>
+        <v>111.5</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="2">
+        <v>5.3369999999999997</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.33100000000000002</v>
+      </c>
+      <c r="G10" s="2">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
+        <v>3</v>
+      </c>
+      <c r="J10" s="2">
+        <v>33</v>
+      </c>
+      <c r="K10" s="2">
+        <v>45</v>
+      </c>
+      <c r="L10" s="2">
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="M10" s="2">
+        <v>-5.7240000000000002</v>
+      </c>
+      <c r="N10" s="2">
+        <v>28.263999999999999</v>
+      </c>
+      <c r="O10" s="2">
+        <v>1273.4000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>46242</v>
+      </c>
+      <c r="B11" s="2">
+        <v>111.203</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="2">
-        <v>6.395</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0.723</v>
-      </c>
-      <c r="G10" s="2">
-        <v>0.089</v>
-      </c>
-      <c r="H10" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="I10" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="J10" s="2">
-        <v>33.0</v>
-      </c>
-      <c r="K10" s="2">
-        <v>35.0</v>
-      </c>
-      <c r="L10" s="2">
-        <v>4.303</v>
-      </c>
-      <c r="M10" s="2">
-        <v>-5.687</v>
-      </c>
-      <c r="N10" s="2">
-        <v>28.746</v>
-      </c>
-      <c r="O10" s="2">
-        <v>1337.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3">
-        <v>46242.0</v>
-      </c>
-      <c r="B11" s="2">
-        <v>111.5</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="E11" s="2">
-        <v>5.337</v>
+        <v>3.9129999999999998</v>
       </c>
       <c r="F11" s="2">
-        <v>0.331</v>
+        <v>0.26900000000000002</v>
       </c>
       <c r="G11" s="2">
-        <v>0.033</v>
+        <v>1.9E-2</v>
       </c>
       <c r="H11" s="2">
-        <v>0.0</v>
+        <v>1E-3</v>
       </c>
       <c r="I11" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J11" s="2">
-        <v>33.0</v>
+        <v>13</v>
       </c>
       <c r="K11" s="2">
-        <v>45.0</v>
+        <v>17</v>
       </c>
       <c r="L11" s="2">
-        <v>4.98</v>
+        <v>4.3090000000000002</v>
       </c>
       <c r="M11" s="2">
-        <v>-5.724</v>
+        <v>-3.8530000000000002</v>
       </c>
       <c r="N11" s="2">
-        <v>28.264</v>
+        <v>28.994</v>
       </c>
       <c r="O11" s="2">
-        <v>1273.4</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>688.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>46242.0</v>
+        <v>46242</v>
       </c>
       <c r="B12" s="2">
-        <v>111.203</v>
+        <v>113.24</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>33</v>
@@ -955,181 +971,134 @@
         <v>19</v>
       </c>
       <c r="E12" s="2">
-        <v>3.913</v>
+        <v>5.5469999999999997</v>
       </c>
       <c r="F12" s="2">
-        <v>0.269</v>
+        <v>0.432</v>
       </c>
       <c r="G12" s="2">
-        <v>0.019</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="H12" s="2">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>3.0</v>
+        <v>2</v>
       </c>
       <c r="J12" s="2">
-        <v>13.0</v>
+        <v>38</v>
       </c>
       <c r="K12" s="2">
-        <v>17.0</v>
+        <v>36</v>
       </c>
       <c r="L12" s="2">
-        <v>4.309</v>
+        <v>4.6390000000000002</v>
       </c>
       <c r="M12" s="2">
-        <v>-3.853</v>
+        <v>-5.367</v>
       </c>
       <c r="N12" s="2">
-        <v>28.994</v>
+        <v>25.895</v>
       </c>
       <c r="O12" s="2">
-        <v>688.3</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>1209.5999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>46242.0</v>
+        <v>46242</v>
       </c>
       <c r="B13" s="2">
-        <v>113.24</v>
+        <v>113.82899999999999</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E13" s="2">
-        <v>5.547</v>
+        <v>6.2510000000000003</v>
       </c>
       <c r="F13" s="2">
-        <v>0.432</v>
+        <v>0.56100000000000005</v>
       </c>
       <c r="G13" s="2">
-        <v>0.004</v>
+        <v>2.3E-2</v>
       </c>
       <c r="H13" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>2.0</v>
+        <v>4</v>
       </c>
       <c r="J13" s="2">
-        <v>38.0</v>
+        <v>37</v>
       </c>
       <c r="K13" s="2">
-        <v>36.0</v>
+        <v>44</v>
       </c>
       <c r="L13" s="2">
-        <v>4.639</v>
+        <v>4.7720000000000002</v>
       </c>
       <c r="M13" s="2">
-        <v>-5.367</v>
+        <v>-6.1020000000000003</v>
       </c>
       <c r="N13" s="2">
-        <v>25.895</v>
+        <v>28.396999999999998</v>
       </c>
       <c r="O13" s="2">
-        <v>1209.6</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>1016.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>46242.0</v>
+        <v>46242</v>
       </c>
       <c r="B14" s="2">
-        <v>113.829</v>
+        <v>112.54300000000001</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E14" s="2">
-        <v>6.251</v>
+        <v>3.9209999999999998</v>
       </c>
       <c r="F14" s="2">
-        <v>0.561</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G14" s="2">
-        <v>0.023</v>
+        <v>2.3E-2</v>
       </c>
       <c r="H14" s="2">
-        <v>0.0</v>
+        <v>0.01</v>
       </c>
       <c r="I14" s="2">
-        <v>4.0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="2">
-        <v>37.0</v>
+        <v>23</v>
       </c>
       <c r="K14" s="2">
-        <v>44.0</v>
+        <v>13</v>
       </c>
       <c r="L14" s="2">
-        <v>4.772</v>
+        <v>4.2869999999999999</v>
       </c>
       <c r="M14" s="2">
-        <v>-6.102</v>
+        <v>-4.0309999999999997</v>
       </c>
       <c r="N14" s="2">
-        <v>28.397</v>
+        <v>30.138999999999999</v>
       </c>
       <c r="O14" s="2">
-        <v>1016.8</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3">
-        <v>46242.0</v>
-      </c>
-      <c r="B15" s="2">
-        <v>112.543</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="2">
-        <v>3.921</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0.28</v>
-      </c>
-      <c r="G15" s="2">
-        <v>0.023</v>
-      </c>
-      <c r="H15" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="I15" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="J15" s="2">
-        <v>23.0</v>
-      </c>
-      <c r="K15" s="2">
-        <v>13.0</v>
-      </c>
-      <c r="L15" s="2">
-        <v>4.287</v>
-      </c>
-      <c r="M15" s="2">
-        <v>-4.031</v>
-      </c>
-      <c r="N15" s="2">
-        <v>30.139</v>
-      </c>
-      <c r="O15" s="2">
         <v>797.2</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>